--- a/two-minute-training-tuesday/episodes/001-excel-dynamic-arrays/demo-workbook-solved.xlsx
+++ b/two-minute-training-tuesday/episodes/001-excel-dynamic-arrays/demo-workbook-solved.xlsx
@@ -11207,7 +11207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:J10"/>
+  <dimension ref="B1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -11221,7 +11221,10 @@
     <col width="26" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="3" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="3" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11259,7 +11262,7 @@
           <t>Powder Line 1</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>Cost centers (typed)</t>
         </is>
@@ -11274,7 +11277,7 @@
         <f>SORT(UNIQUE(ERP_Export[Vendor]))</f>
         <v/>
       </c>
-      <c r="J5" s="9" t="inlineStr">
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t>Powder Line 1</t>
         </is>
@@ -11286,7 +11289,7 @@
           <t>3. Every line for that cost center</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr">
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>Liquid Line 2</t>
         </is>
@@ -11297,28 +11300,28 @@
         <f>FILTER(ERP_Export,ERP_Export[Cost Center]=G4,"No matches")</f>
         <v/>
       </c>
-      <c r="J7" s="9" t="inlineStr">
+      <c r="M7" s="9" t="inlineStr">
         <is>
           <t>Prep &amp; Blast</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="J8" s="9" t="inlineStr">
+      <c r="M8" s="9" t="inlineStr">
         <is>
           <t>Maintenance</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="J9" s="9" t="inlineStr">
+      <c r="M9" s="9" t="inlineStr">
         <is>
           <t>QC Lab</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="J10" s="9" t="inlineStr">
+      <c r="M10" s="9" t="inlineStr">
         <is>
           <t>Shipping</t>
         </is>
